--- a/artfynd/A 8620-2024 artfynd.xlsx
+++ b/artfynd/A 8620-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,47 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>115159119</v>
+        <v>115159215</v>
       </c>
       <c r="B2" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92333</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>4217</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,10 +721,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>576999</v>
+        <v>576992</v>
       </c>
       <c r="R2" t="n">
-        <v>6394939</v>
+        <v>6394972</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,47 +784,46 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>115159051</v>
+        <v>115159250</v>
       </c>
       <c r="B3" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -834,13 +831,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577011</v>
+        <v>577028</v>
       </c>
       <c r="R3" t="n">
-        <v>6394956</v>
+        <v>6394961</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -878,7 +875,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -897,15 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>115159134</v>
+        <v>115158926</v>
       </c>
       <c r="B4" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -945,10 +936,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>576979</v>
+        <v>577026</v>
       </c>
       <c r="R4" t="n">
-        <v>6394910</v>
+        <v>6394948</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,15 +999,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>115159178</v>
+        <v>115158949</v>
       </c>
       <c r="B5" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1056,10 +1042,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>576951</v>
+        <v>577007</v>
       </c>
       <c r="R5" t="n">
-        <v>6394974</v>
+        <v>6394970</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1119,15 +1105,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>115159149</v>
+        <v>115158975</v>
       </c>
       <c r="B6" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1167,10 +1148,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>576959</v>
+        <v>577028</v>
       </c>
       <c r="R6" t="n">
-        <v>6394957</v>
+        <v>6394987</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1230,15 +1211,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>115159227</v>
+        <v>115159001</v>
       </c>
       <c r="B7" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1278,10 +1254,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>576987</v>
+        <v>577019</v>
       </c>
       <c r="R7" t="n">
-        <v>6394946</v>
+        <v>6394995</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1341,15 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>115159201</v>
+        <v>115159008</v>
       </c>
       <c r="B8" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1389,10 +1360,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>576989</v>
+        <v>577019</v>
       </c>
       <c r="R8" t="n">
-        <v>6394966</v>
+        <v>6394965</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1452,51 +1423,42 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>115159250</v>
+        <v>115159028</v>
       </c>
       <c r="B9" t="n">
-        <v>57414</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1504,13 +1466,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>577028</v>
+        <v>577021</v>
       </c>
       <c r="R9" t="n">
-        <v>6394961</v>
+        <v>6394946</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1548,6 +1510,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1566,15 +1529,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>115159063</v>
+        <v>115159043</v>
       </c>
       <c r="B10" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1614,10 +1572,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>577007</v>
+        <v>577026</v>
       </c>
       <c r="R10" t="n">
-        <v>6394958</v>
+        <v>6394935</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1677,50 +1635,42 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>115159215</v>
+        <v>115159051</v>
       </c>
       <c r="B11" t="n">
-        <v>90726</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4217</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1728,10 +1678,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>576992</v>
+        <v>577011</v>
       </c>
       <c r="R11" t="n">
-        <v>6394972</v>
+        <v>6394956</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1791,15 +1741,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>115159103</v>
+        <v>115159063</v>
       </c>
       <c r="B12" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1839,10 +1784,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>577003</v>
+        <v>577007</v>
       </c>
       <c r="R12" t="n">
-        <v>6394972</v>
+        <v>6394958</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1902,15 +1847,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>115158949</v>
+        <v>115159084</v>
       </c>
       <c r="B13" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1950,10 +1890,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>577007</v>
+        <v>577009</v>
       </c>
       <c r="R13" t="n">
-        <v>6394970</v>
+        <v>6394955</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2013,15 +1953,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>115159164</v>
+        <v>115159103</v>
       </c>
       <c r="B14" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2061,10 +1996,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>576971</v>
+        <v>577003</v>
       </c>
       <c r="R14" t="n">
-        <v>6394955</v>
+        <v>6394972</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2124,15 +2059,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>115159028</v>
+        <v>115159119</v>
       </c>
       <c r="B15" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2172,10 +2102,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>577021</v>
+        <v>576999</v>
       </c>
       <c r="R15" t="n">
-        <v>6394946</v>
+        <v>6394939</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2235,15 +2165,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>115159008</v>
+        <v>115159134</v>
       </c>
       <c r="B16" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2283,10 +2208,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>577019</v>
+        <v>576979</v>
       </c>
       <c r="R16" t="n">
-        <v>6394965</v>
+        <v>6394910</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2346,15 +2271,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>115158926</v>
+        <v>115159149</v>
       </c>
       <c r="B17" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2394,10 +2314,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>577026</v>
+        <v>576959</v>
       </c>
       <c r="R17" t="n">
-        <v>6394948</v>
+        <v>6394957</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2457,15 +2377,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>115159084</v>
+        <v>115159164</v>
       </c>
       <c r="B18" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2505,7 +2420,7 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>577009</v>
+        <v>576971</v>
       </c>
       <c r="R18" t="n">
         <v>6394955</v>
@@ -2565,6 +2480,536 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>115159178</v>
+      </c>
+      <c r="B19" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>A 8620, Grönshult, Sm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>576951</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6394974</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Hjorted</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-03-13</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-03-13</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>115159201</v>
+      </c>
+      <c r="B20" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>A 8620, Grönshult, Sm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>576989</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6394966</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Hjorted</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-03-13</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-03-13</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>115159227</v>
+      </c>
+      <c r="B21" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>A 8620, Grönshult, Sm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>576987</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6394946</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Hjorted</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-03-13</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-03-13</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>115159238</v>
+      </c>
+      <c r="B22" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>A 8620, Grönshult, Sm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>577010</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6394978</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Hjorted</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-03-13</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-03-13</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>115309229</v>
+      </c>
+      <c r="B23" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Fagersand, biotopskydd, Sm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>577040</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6394996</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Hjorted</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-03-21</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-03-21</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Ingvor Kasselstrand, Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
